--- a/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3184" uniqueCount="433">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T10:22:16+00:00</t>
+    <t>2026-10-07T08:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1188,7 +1188,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>ORC-23?</t>
@@ -1331,6 +1331,10 @@
   </si>
   <si>
     <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>PID-11</t>
@@ -11521,13 +11525,13 @@
         <v>21</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>99</v>
+        <v>425</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>21</v>
@@ -11538,10 +11542,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11564,17 +11568,17 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>21</v>
@@ -11623,7 +11627,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
